--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-120254</t>
+          <t>I-496458</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021803</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,27 +503,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.0744678</t>
+          <t>-9.0228405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.5768563</t>
+          <t>-78.6190842</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Miguel Grau</t>
+          <t>Jirón Pescadores / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-120255</t>
+          <t>I-45238</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021809</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.0743835</t>
+          <t>-9.0826882</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.5768533</t>
+          <t>-78.5233921</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Miguel Grau</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-261288</t>
+          <t>I-447525</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.0335598</t>
+          <t>-9.0746105</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.5612414</t>
+          <t>-78.5832459</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Camino Real / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-440394</t>
+          <t>I-45252</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-9.074489</t>
+          <t>-9.0743828</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.584174</t>
+          <t>-78.5726598</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AV. CAMINO REAL CON JR. LIBERTAD</t>
+          <t>Avenida Camino Real / Jirón Santa Cruz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-398007</t>
+          <t>I-47446</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.0764895</t>
+          <t>-9.0761557</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-78.5902974</t>
+          <t>-78.5901963</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-438986</t>
+          <t>I-496635</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.0745724</t>
+          <t>-9.0626443</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.5728936</t>
+          <t>-78.5850073</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jr. Santa Cruz</t>
+          <t>Pasaje José Olaya / Pasaje San Martín</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-439031</t>
+          <t>I-46004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.0746853</t>
+          <t>-9.0710088</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.582919</t>
+          <t>-78.5698056</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Ancash</t>
+          <t>Avenida Moquegua / Avenida Perú</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-440277</t>
+          <t>I-439024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-9.0785457</t>
+          <t>-9.0695815</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.5908417</t>
+          <t>-78.5863203</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Prolongación Miguel Grau</t>
+          <t>Avenida Buenos Aires / Jirón Dionisio Derteano</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-447525</t>
+          <t>I-440672</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.0746105</t>
+          <t>-9.0581863</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.5832459</t>
+          <t>-78.5781348</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Camino Real</t>
+          <t>Jirón Unión / Prolongación Avenida Buenos Aires</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-447526</t>
+          <t>I-447088</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021803</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,27 +971,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9.0745958</t>
+          <t>-9.0280188</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-78.5829021</t>
+          <t>-78.6110034</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Ancash</t>
+          <t>Antigua Panamericana Norte / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-45252</t>
+          <t>I-496461</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021803</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.0743828</t>
+          <t>-9.0231491</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-78.5726598</t>
+          <t>-78.6177379</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Santa Cruz</t>
+          <t>Jirón San Martín / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-45302</t>
+          <t>I-496463</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021803</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.0744661</t>
+          <t>-9.021644</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-78.5767093</t>
+          <t>-78.6210718</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Miguel Grau</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-45303</t>
+          <t>I-442250</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>021803</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.0743825</t>
+          <t>-9.0258256</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-78.576708</t>
+          <t>-78.6117522</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jr. Miguel Grau</t>
+          <t>Antigua Panamericana Norte / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-46129</t>
+          <t>I-440277</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.083455</t>
+          <t>-9.0785457</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-78.5734801</t>
+          <t>-78.5908417</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jr. Drenaje / Prolongación Leoncio Prado</t>
+          <t>Prolongación Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1203,786 +1203,6 @@
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>l-46286</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-9.0744815</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-78.5763156</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Avenida Camino Real / Jr. Mariscal Ureta</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>l-46287</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-9.0744</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-78.5763181</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Avenida Camino Real / Jr. Mariscal Ureta</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>l-46406</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-9.0624365</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-78.5853761</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Pasaje Andrés Avelino Cáceres</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>l-46409</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-9.0623786</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-78.5853157</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Jr. Salamanca</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>l-46706</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-9.0749551</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-78.5829886</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Jr. Ancash / Prolongación Alfonso Ugarte</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-47446</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-9.0761557</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-78.5901963</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Avenida José Gálvez / Avenida José Pardo</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-47447</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-9.0761895</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-78.59008</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Avenida José Gálvez / Avenida José Pardo</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-496635</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-9.0626443</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-78.5850073</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Pasaje José Olaya / Pasaje San Martín</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>l-496639</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-9.0623154</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-78.5850213</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Jr. Salamanca / Pasaje San Martín</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-702823</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-9.0765224</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-78.5901801</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Avenida José Gálvez / Avenida José Pardo</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-734309</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-9.03377</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-78.5609469</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-734310</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-9.0336481</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-78.5608616</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-734311</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-9.0339101</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-78.5610449</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>l-734548</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-9.0744778</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-78.5773769</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Avenida Camino Real / Jr. Manuel Seoane</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>l-734549</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-9.0743901</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-78.5773889</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Avenida Camino Real / Jr. Manuel Seoane</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
         <is>
           <t>021801</t>
         </is>

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,58 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-299393</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>021803</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COISHCO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-9.0224445</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-78.6133025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antigua Panamericana Norte / Calle Alfonso Ugarte</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>021801</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Jirón Unión / Prolongación Avenida Buenos Aires</t>
+          <t>Avenida Buenos Aires / Jirón Sucre / Jirón Unión / Prolongación Avenida Buenos Aires</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1255,6 +1255,58 @@
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>021801</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-441296</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>021803</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COISHCO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-9.0217157</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-78.6144612</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antigua Panamericana Norte / Avenida Villa del Mar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>021801</t>
         </is>

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-496458</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-9.0228405</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-45238</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>021809</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-9.0826882</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-447525</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-9.0746105</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-45252</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-9.0743828</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-47446</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-9.0761557</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-496635</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-9.0626443</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-46004</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-9.0710088</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-439024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-9.0695815</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-440672</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-9.0581863</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-447088</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-9.0280188</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-496461</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-9.0231491</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-496463</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-9.021644</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-442250</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-9.0258256</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-440277</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-9.0785457</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-299393</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-9.0224445</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-441296</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>021803</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-9.0217157</t>
@@ -1304,11 +1224,6 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/Intersecciones/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-496458</t>
+          <t>I-496635</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.0228405</t>
+          <t>-9.0626443</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.6190842</t>
+          <t>-78.5850073</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Pescadores / Calle s / n</t>
+          <t>Pasaje José Olaya / Pasaje San Martín</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-45238</t>
+          <t>I-496463</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.0826882</t>
+          <t>-9.021644</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.5233921</t>
+          <t>-78.6210718</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-447525</t>
+          <t>I-496461</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.0746105</t>
+          <t>-9.0231491</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.5832459</t>
+          <t>-78.6177379</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Calle s / n</t>
+          <t>Jirón San Martín / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-45252</t>
+          <t>I-496458</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-9.0743828</t>
+          <t>-9.0228405</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.5726598</t>
+          <t>-78.6190842</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Jirón Santa Cruz</t>
+          <t>Jirón Pescadores / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-496635</t>
+          <t>I-46004</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.0626443</t>
+          <t>-9.0710088</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.5850073</t>
+          <t>-78.5698056</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pasaje José Olaya / Pasaje San Martín</t>
+          <t>Avenida Moquegua / Avenida Perú</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-46004</t>
+          <t>I-45252</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.0710088</t>
+          <t>-9.0743828</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.5698056</t>
+          <t>-78.5726598</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Moquegua / Avenida Perú</t>
+          <t>Avenida Camino Real / Jirón Santa Cruz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-439024</t>
+          <t>I-45238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-9.0695815</t>
+          <t>-9.0826882</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.5863203</t>
+          <t>-78.5233921</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Buenos Aires / Jirón Dionisio Derteano</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-440672</t>
+          <t>I-447525</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.0581863</t>
+          <t>-9.0746105</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.5781348</t>
+          <t>-78.5832459</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Buenos Aires / Jirón Sucre / Jirón Unión / Prolongación Avenida Buenos Aires</t>
+          <t>Avenida Camino Real / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-496461</t>
+          <t>I-442250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.0231491</t>
+          <t>-9.0258256</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-78.6177379</t>
+          <t>-78.6117522</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jirón San Martín / Calle s / n</t>
+          <t>Antigua Panamericana Norte / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-496463</t>
+          <t>I-441296</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.021644</t>
+          <t>-9.0217157</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-78.6210718</t>
+          <t>-78.6144612</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Antigua Panamericana Norte / Avenida Villa del Mar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-442250</t>
+          <t>I-440672</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.0258256</t>
+          <t>-9.0581863</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-78.6117522</t>
+          <t>-78.5781348</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Norte / Calle s / n</t>
+          <t>Jirón Unión / Prolongación Avenida Buenos Aires</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-299393</t>
+          <t>I-439024</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-9.0224445</t>
+          <t>-9.0695815</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.6133025</t>
+          <t>-78.5863203</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Norte / Calle Alfonso Ugarte</t>
+          <t>Avenida Buenos Aires / Jirón Dionisio Derteano</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-441296</t>
+          <t>I-299393</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-9.0217157</t>
+          <t>-9.0224445</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-78.6144612</t>
+          <t>-78.6133025</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Norte / Avenida Villa del Mar</t>
+          <t>Antigua Panamericana Norte / Calle Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
